--- a/DataAnalytics/week-01/Ex2B_data_roundup.xlsx
+++ b/DataAnalytics/week-01/Ex2B_data_roundup.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\alsso\Desktop\Hamzah123456-data-analytics\DataAnalytics\week-01\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A68FE43-A01C-4CE3-9889-4F45CCE3E8BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9DDC3AF0-E321-4A8A-AEBC-7A87175A8B9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="15370" xr2:uid="{0F7A91C4-EFF4-4C25-978B-B6AE7E58A8D7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{0F7A91C4-EFF4-4C25-978B-B6AE7E58A8D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,12 +35,79 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+  <si>
+    <t>Gmail</t>
+  </si>
+  <si>
+    <t>4 years</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Google Takeout &gt; Select Mail</t>
+  </si>
+  <si>
+    <t>.mbox or .zip</t>
+  </si>
+  <si>
+    <t>Communication</t>
+  </si>
+  <si>
+    <t>TikTok</t>
+  </si>
+  <si>
+    <t>2 years</t>
+  </si>
+  <si>
+    <t>Social Media</t>
+  </si>
+  <si>
+    <t>Profile &gt; Menu &gt; Settings and Privacy &gt;  Account &gt; Download your data &gt; Choose info and format &gt; Request Data</t>
+  </si>
+  <si>
+    <t>.json or .txt</t>
+  </si>
+  <si>
+    <t>Instagram</t>
+  </si>
+  <si>
+    <t>3 Years</t>
+  </si>
+  <si>
+    <t>Account &gt; Information and Permissions &gt; download/export information</t>
+  </si>
+  <si>
+    <t>.json or .html</t>
+  </si>
+  <si>
+    <t>Instagram lets you export a copy of your information.</t>
+  </si>
+  <si>
+    <t>File is available for a limited time.</t>
+  </si>
+  <si>
+    <t>Download may include all email history.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -63,13 +130,16 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -83,6 +153,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -402,9 +476,329 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AF9B82C-AE71-40E1-8759-E57389BDF975}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="12.54296875" customWidth="1"/>
+    <col min="2" max="2" width="19.26953125" customWidth="1"/>
+    <col min="3" max="3" width="13.36328125" customWidth="1"/>
+    <col min="4" max="4" width="12.1796875" customWidth="1"/>
+    <col min="5" max="5" width="98.08984375" customWidth="1"/>
+    <col min="6" max="6" width="23.1796875" customWidth="1"/>
+    <col min="7" max="7" width="30.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101006BAB7F1D75092C43A80735B994755528" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="10fa938135b808f17595af21c7675450">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="b275f972-a0ec-44ed-acfc-93b347ca42d1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="8fffa6ddc6845d0759a1205da59a7e7c" ns3:_="">
+    <xsd:import namespace="b275f972-a0ec-44ed-acfc-93b347ca42d1"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns3:_activity" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceSystemTags" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:MediaLengthInSeconds" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="b275f972-a0ec-44ed-acfc-93b347ca42d1" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceDateTaken" ma:index="8" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="_activity" ma:index="12" nillable="true" ma:displayName="_activity" ma:hidden="true" ma:internalName="_activity">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSystemTags" ma:index="13" nillable="true" ma:displayName="MediaServiceSystemTags" ma:hidden="true" ma:internalName="MediaServiceSystemTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="17" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="b275f972-a0ec-44ed-acfc-93b347ca42d1" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DE170B9C-E8F6-4FC0-9A33-E433674E9EDE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4114C9B2-6AFB-4CBD-B82D-5B678CE451A2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b275f972-a0ec-44ed-acfc-93b347ca42d1"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B5EBF8B-A672-4003-886B-6936ED0DE7F1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="b275f972-a0ec-44ed-acfc-93b347ca42d1"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>